--- a/Chris/Test/test_data.xlsx
+++ b/Chris/Test/test_data.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\b1810\Desktop\coding\Cellpose-Image-Analysis\Chris\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECD7B89F-1931-43A4-ACF4-399AF7A2506D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F715803-E643-420F-892D-C7D967D2AD0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{C26AED81-6654-44AB-A5A7-2F6EE1563971}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -556,4 +557,13 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70E6FF4B-617A-4379-84C9-76817C9315BF}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>